--- a/docs/exports/DUBAI_remaining_20261012.xlsx
+++ b/docs/exports/DUBAI_remaining_20261012.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 単価だけ要る 55品" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 名前か単位が不一致 10品" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 支店別 PAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 単価を入れる" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 支店別 PAR" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +37,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +54,11 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +72,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,14 +445,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +480,16 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Daily Inventory の原価</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>参考: ×1000 した値</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Unit price (AED) ←記入</t>
         </is>
       </c>
@@ -494,7 +511,9 @@
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="3" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -513,7 +532,9 @@
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="3" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -532,7 +553,9 @@
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -555,7 +578,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -578,7 +603,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -597,7 +624,9 @@
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="3" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -620,7 +649,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -630,12 +661,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Shoyu Veg Ramen Soup</t>
+          <t>Shio Yakisoba Sauce</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -643,7 +674,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -653,12 +686,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Tofu Veg Meat</t>
+          <t>Shoyu Veg Ramen Soup</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -666,7 +699,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -676,12 +711,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Volcano veg Ramen Soup</t>
+          <t>Tofu Veg Meat</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -689,22 +724,24 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CK PREPARED FOODS</t>
+          <t>AVS WAREHOUSE ITEMS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Batter Flour</t>
+          <t>Volcano veg Ramen Soup</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -712,7 +749,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -722,12 +761,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cheese &amp; Mushroom Momo (1pc)</t>
+          <t>Batter Flour</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -735,7 +774,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -745,12 +786,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Chicken Dumpling</t>
+          <t>Beans sprout namul</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -758,7 +799,13 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n"/>
+      <c r="E14" s="4" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -768,7 +815,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Chicken Steam Dumplings</t>
+          <t>Cheese &amp; Mushroom Momo (1pc)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -781,7 +828,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -791,12 +840,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Gyoza wrapper</t>
+          <t>Chicken Dumpling</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PKT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -804,7 +853,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -814,7 +865,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Mixed Veggie Momo</t>
+          <t>Chicken Steam Dumplings</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -827,7 +878,9 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -837,12 +890,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Shredded Cut Beef</t>
+          <t>Chinese Cabbage Kimchi</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PKT</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -850,7 +903,13 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n"/>
+      <c r="E18" s="4" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -860,12 +919,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Shrimp Steam Dumplings</t>
+          <t>Cucumber Kimchi</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -873,7 +932,13 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n"/>
+      <c r="E19" s="4" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -883,7 +948,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sliced Beef for Bento</t>
+          <t>Gyoza wrapper</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -896,22 +961,24 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HOT SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Green Curry Sauce</t>
+          <t>Mixed Veggie Momo</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PKT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -919,17 +986,19 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HOT SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Momo sauce hot</t>
+          <t>Radish Kimchi</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -942,17 +1011,23 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="4" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HOT SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Pickle momo sauce</t>
+          <t>Radish namul</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -965,17 +1040,23 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n"/>
+      <c r="E23" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HOT SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Spicy Korean Chicken Sauce</t>
+          <t>Seasoned Shiitake Mushroom</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -988,17 +1069,23 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n"/>
+      <c r="E24" s="4" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SUSHI SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Beets Sauce</t>
+          <t>Sesame Black</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1011,17 +1098,23 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n"/>
+      <c r="E25" s="4" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SUSHI SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Hawaiian Poke Sauce</t>
+          <t>Sesame White</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1034,22 +1127,28 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n"/>
+      <c r="E26" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SUSHI SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Italian poke sauce</t>
+          <t>Shredded Cut Beef</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>PKT</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1057,22 +1156,24 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SUSHI SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Spicy Miso Mayo</t>
+          <t>Shrimp Steam Dumplings</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1080,22 +1181,24 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SUSHI SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Tuna mayo</t>
+          <t>Sliced Beef for Bento</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>PKT</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1103,17 +1206,19 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SUSHI SAUCE</t>
+          <t>CK PREPARED FOODS</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Wasabi Poke Sauce</t>
+          <t>Spicy beans sprout namul</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1126,501 +1231,2042 @@
           <t>CK</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n"/>
+      <c r="E30" s="4" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2oz Cup with Lid</t>
+          <t>BBQ sauce</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ALUMINUM FOIL</t>
+          <t>Chicken Teriyaki Sauce</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Bento 8 Box</t>
+          <t>Cho gochujang sauce</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Black Container</t>
+          <t>Fried Noodle Sauce</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Multi Purpose Lighter</t>
+          <t>Fried Rice Sauce</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>New Box 12 (Container)</t>
+          <t>Green Curry Sauce</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="3" t="n"/>
+          <t>PKT</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>New Box 24 (Container)</t>
+          <t>Honey Butter</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Film</t>
+          <t>Mi Goreng Sauce</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>PKT</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Sticker (BBQ)</t>
+          <t>Momo sauce hot</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Sticker (Salmon Teriyaki)</t>
+          <t>Nasi Goreng Sauce</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Sticker (Spicy Tuna)</t>
+          <t>Pickle momo sauce</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Sticker (Tuna Mayo)</t>
+          <t>Soya Garlic</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Piping bag</t>
+          <t>Spicy Edamame Sauce</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Ramen Bowl</t>
+          <t>Spicy Korean Chicken Sauce</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Ramen Sticker (Red Hot)</t>
+          <t>Spicy yakisoba sauce</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Ramen Sticker(Rich Miso)</t>
+          <t>Sweet Buffalo sauce</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>HOT SAUCE</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Ramen Sticker(Volcano)</t>
+          <t>You Ling Zhi Sauce</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>SAFCO</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ramne Sticker(Umami Shoyu)</t>
+          <t>Food Color Green</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>BTL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="3" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>SAFCO</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Sanitize Tablet</t>
+          <t>Food Colour REd</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>BTL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="3" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>SAFCO</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Soup Bowl 20oz</t>
+          <t>HONTERI MIRIN - MIZKAN</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="3" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>SUNBERRY</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Sticker Round</t>
+          <t>BABY ASPARAGUS 1pkt=100g</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="3" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>SUNBERRY</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Tape</t>
+          <t>Bean Sprout</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="3" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>SUSHI SAUCE</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Tape Dispenser</t>
+          <t>Beets Sauce</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>SUSHI SAUCE</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Temaki Film</t>
+          <t>Beijin Sweet Sauce</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE ITEMS</t>
+          <t>SUSHI SAUCE</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Temaki instruction paper</t>
+          <t>Cheesy Sauce</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="3" t="n"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Crab Stick Salad Sauce</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Hawaiian Poke Sauce</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Hot Mayo</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Italian poke sauce</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Korean Star Sauce(NEW)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Mango sauce</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>MIso Sauce</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Poke Sauce</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Rich Honey Mustard Sauce</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Rich Lemon Cream Sauce</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Rich Sesame Mayo</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Rich Truffle Sauce</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Silky Wasabi Mayo</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Sirach Mayo</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Spicy Miso Mayo</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Spicy Provance</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Spicy Teriyaki Sauce</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Spicy Tuna Mix</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Suhsi Vinegar</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Sweet Mayo</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Sweet Sauce</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Tuna mayo</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Velvety Sauce</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Wasabi Poke Sauce</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Yang Nyomeng Sauce</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SUSHI SAUCE</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Zesty Sweet Sauce</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TASTE MASTERS</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>MENMA BAMBOO SHOOT</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>TASTE MASTERS</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>TAKWAN TARO 500g</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>PKT</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
           <t>WAREHOUSE ITEMS</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2oz Cup with Lid</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ALUMINUM FOIL</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Bento 8 Box</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Black Container</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Multi Purpose Lighter</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>New Box 12 (Container)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>New Box 24 (Container)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Onigiri Film</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>PKT</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Onigiri Sticker (BBQ)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Onigiri Sticker (Salmon Teriyaki)</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="3" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Onigiri Sticker (Spicy Tuna)</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="3" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Onigiri Sticker (Tuna Mayo)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="n"/>
+      <c r="G95" s="3" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Piping bag</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="3" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Plastick Cutlerly (L)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="3" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Plastick Cutlerly (S)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="3" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Ramen Bowl</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n"/>
+      <c r="G99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Ramen Sticker (Red Hot)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="3" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Ramen Sticker(Rich Miso)</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="3" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Ramen Sticker(Volcano)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Ramne Sticker(Umami Shoyu)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Sanitize Tablet</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Soup Bowl 20oz</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="n"/>
+      <c r="F105" s="2" t="n"/>
+      <c r="G105" s="3" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Sticker Round</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="3" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Tape</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="3" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Tape Dispenser</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n"/>
+      <c r="G108" s="3" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Temaki Film</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="3" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Temaki instruction paper</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="3" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ITEMS</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Thermal Paper Small</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>ROLL</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="3" t="n"/>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="n"/>
+      <c r="F111" s="2" t="n"/>
+      <c r="G111" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1628,372 +3274,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>棚卸しの名前</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>棚卸し単位</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>カタログの行</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>カタログ単位</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>似た既存の行</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>一致度</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>AVS WAREHOUSE ITEMS</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Shio Yakisoba Sauce</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>行なし</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>YAKISOBA SAUCE</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SAFCO</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Food Color Green</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>BTL</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>FOOD COLOR GREEN</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>FOOD COLOR GREEN</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SAFCO</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Food Colour REd</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>BTL</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>行なし</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>FOOD COLOUR RED 28ML - NATCO</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SAFCO</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>HONTERI MIRIN - MIZKAN</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>LTR</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>行なし</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>HONTERI MIRIN-MIZKAN</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SUNBERRY</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>BABY ASPARAGUS 1pkt=100g</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>行なし</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>BABY ASPARAGUS (1pkt=100g)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SUNBERRY</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Bean Sprout</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>行なし</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>BEAN SPROUTS</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TASTE MASTERS</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>MENMA BAMBOO SHOOT</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>行なし</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>MENMA BAMBOO SHOOT 1Kg</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TASTE MASTERS</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>TAKWAN TARO 500g</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>PKT</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>TAKWAN TARO 500g</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>TAKWAN TARO 500g</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>WAREHOUSE ITEMS</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Plastick Cutlerly (L)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>行なし</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>WAREHOUSE ITEMS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Plastick Cutlerly (S)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>行なし</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/exports/DUBAI_remaining_20261012.xlsx
+++ b/docs/exports/DUBAI_remaining_20261012.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,19 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00999999"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00999999"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +75,11 @@
         <fgColor rgb="002E5C8A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -77,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -90,6 +106,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3291,7 +3312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M277"/>
+  <dimension ref="A1:N277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3307,6 +3328,7 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3336,6 +3358,11 @@
           <t>AL BARSHA</t>
         </is>
       </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
+          <t>n/a = CK品。刻みはカタログ側（品目に1つ）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -3403,6 +3430,11 @@
           <t>STEP</t>
         </is>
       </c>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>Ordered from</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3450,6 +3482,11 @@
         </is>
       </c>
       <c r="M3" s="3" t="n"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3497,6 +3534,11 @@
         </is>
       </c>
       <c r="M4" s="3" t="n"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3544,6 +3586,11 @@
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3564,25 +3611,50 @@
       <c r="D6" s="2" t="n">
         <v>82.08199999999999</v>
       </c>
-      <c r="E6" s="3" t="n"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="n">
         <v>73.619</v>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="n">
         <v>227.5</v>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="n">
         <v>222.95</v>
       </c>
-      <c r="K6" s="3" t="n"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M6" s="3" t="n"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3603,23 +3675,48 @@
       <c r="D7" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="E7" s="3" t="n"/>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="n">
         <v>42.77</v>
       </c>
-      <c r="G7" s="3" t="n"/>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="n">
         <v>23.296</v>
       </c>
-      <c r="I7" s="3" t="n"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="n">
         <v>21.84</v>
       </c>
-      <c r="K7" s="3" t="n"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="M7" s="3" t="n"/>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3642,31 +3739,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M8" s="3" t="n"/>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3687,23 +3809,48 @@
       <c r="D9" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E9" s="3" t="n"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="n">
         <v>285.285</v>
       </c>
-      <c r="G9" s="3" t="n"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="n">
         <v>1001</v>
       </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="n">
         <v>546</v>
       </c>
-      <c r="K9" s="3" t="n"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="n">
         <v>500.5</v>
       </c>
-      <c r="M9" s="3" t="n"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3724,23 +3871,48 @@
       <c r="D10" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="E10" s="3" t="n"/>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n">
         <v>25.48</v>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="I10" s="3" t="n"/>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="n">
         <v>22.295</v>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="M10" s="3" t="n"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3786,6 +3958,11 @@
         <v>182</v>
       </c>
       <c r="M11" s="3" t="n"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Ramen ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3833,6 +4010,11 @@
         </is>
       </c>
       <c r="M12" s="3" t="n"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3853,23 +4035,48 @@
       <c r="D13" s="2" t="n">
         <v>79.17</v>
       </c>
-      <c r="E13" s="3" t="n"/>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="n">
         <v>74.16500000000001</v>
       </c>
-      <c r="G13" s="3" t="n"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="n">
         <v>76.804</v>
       </c>
-      <c r="I13" s="3" t="n"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="n">
         <v>82.81</v>
       </c>
-      <c r="K13" s="3" t="n"/>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="n">
         <v>13.65</v>
       </c>
-      <c r="M13" s="3" t="n"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3890,23 +4097,48 @@
       <c r="D14" s="2" t="n">
         <v>364</v>
       </c>
-      <c r="E14" s="3" t="n"/>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="n">
         <v>273</v>
       </c>
-      <c r="I14" s="3" t="n"/>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="K14" s="3" t="n"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="M14" s="3" t="n"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3927,23 +4159,48 @@
       <c r="D15" s="2" t="n">
         <v>31.85</v>
       </c>
-      <c r="E15" s="3" t="n"/>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="n">
         <v>25.48</v>
       </c>
-      <c r="G15" s="3" t="n"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="n">
         <v>22.295</v>
       </c>
-      <c r="I15" s="3" t="n"/>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="K15" s="3" t="n"/>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L15" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="M15" s="3" t="n"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3964,23 +4221,48 @@
       <c r="D16" s="2" t="n">
         <v>40.95</v>
       </c>
-      <c r="E16" s="3" t="n"/>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n">
         <v>54.6</v>
       </c>
-      <c r="G16" s="3" t="n"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="I16" s="3" t="n"/>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="n">
         <v>35.49</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="n">
         <v>14.56</v>
       </c>
-      <c r="M16" s="3" t="n"/>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4003,31 +4285,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n"/>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I17" s="3" t="n"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n"/>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M17" s="3" t="n"/>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4050,31 +4357,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n"/>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I18" s="3" t="n"/>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M18" s="3" t="n"/>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4095,23 +4427,48 @@
       <c r="D19" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="E19" s="3" t="n"/>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="n">
         <v>72.072</v>
       </c>
-      <c r="G19" s="3" t="n"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="n">
         <v>10.374</v>
       </c>
-      <c r="I19" s="3" t="n"/>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="n">
         <v>11.102</v>
       </c>
-      <c r="K19" s="3" t="n"/>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="M19" s="3" t="n"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4132,25 +4489,50 @@
       <c r="D20" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="E20" s="3" t="n"/>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n">
         <v>45.773</v>
       </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="I20" s="3" t="n"/>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="n">
         <v>54.6</v>
       </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M20" s="3" t="n"/>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4171,23 +4553,48 @@
       <c r="D21" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="E21" s="3" t="n"/>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="I21" s="3" t="n"/>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="K21" s="3" t="n"/>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="n">
         <v>13.65</v>
       </c>
-      <c r="M21" s="3" t="n"/>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4208,23 +4615,48 @@
       <c r="D22" s="2" t="n">
         <v>22.75</v>
       </c>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="G22" s="3" t="n"/>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="n">
         <v>13.65</v>
       </c>
-      <c r="I22" s="3" t="n"/>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="K22" s="3" t="n"/>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="n">
         <v>13.65</v>
       </c>
-      <c r="M22" s="3" t="n"/>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4270,6 +4702,11 @@
         </is>
       </c>
       <c r="M23" s="3" t="n"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4307,6 +4744,11 @@
         <v>1820</v>
       </c>
       <c r="M24" s="3" t="n"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4344,6 +4786,11 @@
         <v>455.91</v>
       </c>
       <c r="M25" s="3" t="n"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4381,6 +4828,11 @@
         <v>1.82</v>
       </c>
       <c r="M26" s="3" t="n"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4418,6 +4870,11 @@
         <v>1.365</v>
       </c>
       <c r="M27" s="3" t="n"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4455,6 +4912,11 @@
         <v>8.19</v>
       </c>
       <c r="M28" s="3" t="n"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4492,6 +4954,11 @@
         <v>5.096</v>
       </c>
       <c r="M29" s="3" t="n"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4539,6 +5006,11 @@
         </is>
       </c>
       <c r="M30" s="3" t="n"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4578,6 +5050,11 @@
         <v>0.91</v>
       </c>
       <c r="M31" s="3" t="n"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Chef Middle East LLC</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4600,31 +5077,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n"/>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n"/>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I32" s="3" t="n"/>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K32" s="3" t="n"/>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M32" s="3" t="n"/>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4645,23 +5147,48 @@
       <c r="D33" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="E33" s="3" t="n"/>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="n">
         <v>2821</v>
       </c>
-      <c r="G33" s="3" t="n"/>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="I33" s="3" t="n"/>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="n">
         <v>1342.796</v>
       </c>
-      <c r="K33" s="3" t="n"/>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="M33" s="3" t="n"/>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4682,23 +5209,48 @@
       <c r="D34" s="2" t="n">
         <v>2457</v>
       </c>
-      <c r="E34" s="3" t="n"/>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="n">
         <v>5642</v>
       </c>
-      <c r="G34" s="3" t="n"/>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="n">
         <v>2730</v>
       </c>
-      <c r="I34" s="3" t="n"/>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="n">
         <v>2678.676</v>
       </c>
-      <c r="K34" s="3" t="n"/>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="M34" s="3" t="n"/>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4721,31 +5273,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n"/>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n"/>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K35" s="3" t="n"/>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M35" s="3" t="n"/>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4766,23 +5343,48 @@
       <c r="D36" s="2" t="n">
         <v>536.9</v>
       </c>
-      <c r="E36" s="3" t="n"/>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="n">
         <v>305.76</v>
       </c>
-      <c r="G36" s="3" t="n"/>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="n">
         <v>27.3</v>
       </c>
-      <c r="I36" s="3" t="n"/>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="n">
         <v>524.16</v>
       </c>
-      <c r="K36" s="3" t="n"/>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="n">
         <v>29.12</v>
       </c>
-      <c r="M36" s="3" t="n"/>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4805,31 +5407,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n"/>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n"/>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I37" s="3" t="n"/>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K37" s="3" t="n"/>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M37" s="3" t="n"/>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4852,25 +5479,50 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n"/>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="n">
         <v>136.5</v>
       </c>
-      <c r="G38" s="3" t="n"/>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="n">
         <v>114.66</v>
       </c>
-      <c r="I38" s="3" t="n"/>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="n">
         <v>88.452</v>
       </c>
-      <c r="K38" s="3" t="n"/>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M38" s="3" t="n"/>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4891,23 +5543,48 @@
       <c r="D39" s="2" t="n">
         <v>2502.5</v>
       </c>
-      <c r="E39" s="3" t="n"/>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="n">
         <v>3731</v>
       </c>
-      <c r="G39" s="3" t="n"/>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="n">
         <v>3344.25</v>
       </c>
-      <c r="I39" s="3" t="n"/>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="n">
         <v>2730</v>
       </c>
-      <c r="K39" s="3" t="n"/>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4930,31 +5607,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n"/>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n"/>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I40" s="3" t="n"/>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K40" s="3" t="n"/>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M40" s="3" t="n"/>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4977,23 +5679,48 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n"/>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="n">
         <v>19.565</v>
       </c>
-      <c r="G41" s="3" t="n"/>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="n">
         <v>17.836</v>
       </c>
-      <c r="I41" s="3" t="n"/>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="n">
         <v>17.836</v>
       </c>
-      <c r="K41" s="3" t="n"/>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="M41" s="3" t="n"/>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -5014,23 +5741,48 @@
       <c r="D42" s="2" t="n">
         <v>3640</v>
       </c>
-      <c r="E42" s="3" t="n"/>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="n">
         <v>3731</v>
       </c>
-      <c r="G42" s="3" t="n"/>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="n">
         <v>2730</v>
       </c>
-      <c r="I42" s="3" t="n"/>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="n">
         <v>3549</v>
       </c>
-      <c r="K42" s="3" t="n"/>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="M42" s="3" t="n"/>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -5051,23 +5803,48 @@
       <c r="D43" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="E43" s="3" t="n"/>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="n">
         <v>2730</v>
       </c>
-      <c r="G43" s="3" t="n"/>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="n">
         <v>2393.3</v>
       </c>
-      <c r="I43" s="3" t="n"/>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="K43" s="3" t="n"/>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="M43" s="3" t="n"/>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -5090,27 +5867,52 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n"/>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="n">
         <v>18.564</v>
       </c>
-      <c r="G44" s="3" t="n"/>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I44" s="3" t="n"/>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="n">
         <v>5.46</v>
       </c>
-      <c r="K44" s="3" t="n"/>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M44" s="3" t="n"/>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -5131,23 +5933,48 @@
       <c r="D45" s="2" t="n">
         <v>20.93</v>
       </c>
-      <c r="E45" s="3" t="n"/>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="n">
         <v>22.386</v>
       </c>
-      <c r="G45" s="3" t="n"/>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="n">
         <v>30.576</v>
       </c>
-      <c r="I45" s="3" t="n"/>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="n">
         <v>23.569</v>
       </c>
-      <c r="K45" s="3" t="n"/>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="n">
         <v>19.656</v>
       </c>
-      <c r="M45" s="3" t="n"/>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5170,31 +5997,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E46" s="3" t="n"/>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n"/>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I46" s="3" t="n"/>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M46" s="3" t="n"/>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -5215,23 +6067,48 @@
       <c r="D47" s="2" t="n">
         <v>2730</v>
       </c>
-      <c r="E47" s="3" t="n"/>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="n">
         <v>3640</v>
       </c>
-      <c r="G47" s="3" t="n"/>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="n">
         <v>2095.73</v>
       </c>
-      <c r="I47" s="3" t="n"/>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="K47" s="3" t="n"/>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L47" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="M47" s="3" t="n"/>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5252,23 +6129,48 @@
       <c r="D48" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="E48" s="3" t="n"/>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="n">
         <v>3230.5</v>
       </c>
-      <c r="G48" s="3" t="n"/>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="n">
         <v>1319.5</v>
       </c>
-      <c r="I48" s="3" t="n"/>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="K48" s="3" t="n"/>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L48" s="2" t="n">
         <v>2593.5</v>
       </c>
-      <c r="M48" s="3" t="n"/>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -5289,23 +6191,48 @@
       <c r="D49" s="2" t="n">
         <v>23.114</v>
       </c>
-      <c r="E49" s="3" t="n"/>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="n">
         <v>27.664</v>
       </c>
-      <c r="G49" s="3" t="n"/>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="n">
         <v>27.3</v>
       </c>
-      <c r="I49" s="3" t="n"/>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="n">
         <v>24.479</v>
       </c>
-      <c r="K49" s="3" t="n"/>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L49" s="2" t="n">
         <v>14.469</v>
       </c>
-      <c r="M49" s="3" t="n"/>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5326,23 +6253,48 @@
       <c r="D50" s="2" t="n">
         <v>4.55</v>
       </c>
-      <c r="E50" s="3" t="n"/>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="n">
         <v>10.92</v>
       </c>
-      <c r="G50" s="3" t="n"/>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="n">
         <v>7.28</v>
       </c>
-      <c r="I50" s="3" t="n"/>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="n">
         <v>4.55</v>
       </c>
-      <c r="K50" s="3" t="n"/>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="n">
         <v>4.55</v>
       </c>
-      <c r="M50" s="3" t="n"/>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5363,23 +6315,48 @@
       <c r="D51" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="E51" s="3" t="n"/>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="n">
         <v>2093</v>
       </c>
-      <c r="G51" s="3" t="n"/>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="n">
         <v>2047.5</v>
       </c>
-      <c r="I51" s="3" t="n"/>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="n">
         <v>2730</v>
       </c>
-      <c r="K51" s="3" t="n"/>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L51" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="M51" s="3" t="n"/>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5400,23 +6377,48 @@
       <c r="D52" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="E52" s="3" t="n"/>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="G52" s="3" t="n"/>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="n">
         <v>864.5</v>
       </c>
-      <c r="I52" s="3" t="n"/>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="n">
         <v>891.8</v>
       </c>
-      <c r="K52" s="3" t="n"/>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L52" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M52" s="3" t="n"/>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5437,23 +6439,48 @@
       <c r="D53" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="E53" s="3" t="n"/>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="G53" s="3" t="n"/>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="I53" s="3" t="n"/>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="n">
         <v>882.7</v>
       </c>
-      <c r="K53" s="3" t="n"/>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L53" s="2" t="n">
         <v>227.5</v>
       </c>
-      <c r="M53" s="3" t="n"/>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5476,31 +6503,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E54" s="3" t="n"/>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n"/>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I54" s="3" t="n"/>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K54" s="3" t="n"/>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M54" s="3" t="n"/>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5523,31 +6575,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E55" s="3" t="n"/>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G55" s="3" t="n"/>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I55" s="3" t="n"/>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K55" s="3" t="n"/>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M55" s="3" t="n"/>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5570,31 +6647,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E56" s="3" t="n"/>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n"/>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I56" s="3" t="n"/>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K56" s="3" t="n"/>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M56" s="3" t="n"/>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5615,23 +6717,48 @@
       <c r="D57" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="E57" s="3" t="n"/>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="n">
         <v>3003</v>
       </c>
-      <c r="G57" s="3" t="n"/>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="n">
         <v>1114.75</v>
       </c>
-      <c r="I57" s="3" t="n"/>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="K57" s="3" t="n"/>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L57" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="M57" s="3" t="n"/>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5652,23 +6779,48 @@
       <c r="D58" s="2" t="n">
         <v>7.28</v>
       </c>
-      <c r="E58" s="3" t="n"/>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="n">
         <v>12.285</v>
       </c>
-      <c r="G58" s="3" t="n"/>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="I58" s="3" t="n"/>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="K58" s="3" t="n"/>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="M58" s="3" t="n"/>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5706,6 +6858,11 @@
         <v>25.844</v>
       </c>
       <c r="M59" s="3" t="n"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>FRESHTOHOME FOODS (S.P.S - L.L.C)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5753,6 +6910,11 @@
         </is>
       </c>
       <c r="M60" s="3" t="n"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>FRESHTOHOME FOODS (S.P.S - L.L.C)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5790,6 +6952,11 @@
         <v>4.095</v>
       </c>
       <c r="M61" s="3" t="n"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>FRESHTOHOME FOODS (S.P.S - L.L.C)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5810,23 +6977,48 @@
       <c r="D62" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E62" s="3" t="n"/>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="n">
         <v>1456</v>
       </c>
-      <c r="G62" s="3" t="n"/>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="I62" s="3" t="n"/>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="n">
         <v>887.25</v>
       </c>
-      <c r="K62" s="3" t="n"/>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="n">
         <v>637</v>
       </c>
-      <c r="M62" s="3" t="n"/>
+      <c r="M62" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5847,23 +7039,48 @@
       <c r="D63" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E63" s="3" t="n"/>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="G63" s="3" t="n"/>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="n">
         <v>889.98</v>
       </c>
-      <c r="I63" s="3" t="n"/>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="n">
         <v>677.95</v>
       </c>
-      <c r="K63" s="3" t="n"/>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="n">
         <v>644.28</v>
       </c>
-      <c r="M63" s="3" t="n"/>
+      <c r="M63" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5884,23 +7101,48 @@
       <c r="D64" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E64" s="3" t="n"/>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="n">
         <v>2320.5</v>
       </c>
-      <c r="G64" s="3" t="n"/>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="n">
         <v>1114.75</v>
       </c>
-      <c r="I64" s="3" t="n"/>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="K64" s="3" t="n"/>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M64" s="3" t="n"/>
+      <c r="M64" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5921,23 +7163,48 @@
       <c r="D65" s="2" t="n">
         <v>796.25</v>
       </c>
-      <c r="E65" s="3" t="n"/>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="n">
         <v>1911</v>
       </c>
-      <c r="G65" s="3" t="n"/>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="I65" s="3" t="n"/>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="n">
         <v>1107.379</v>
       </c>
-      <c r="K65" s="3" t="n"/>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L65" s="2" t="n">
         <v>657.02</v>
       </c>
-      <c r="M65" s="3" t="n"/>
+      <c r="M65" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5958,23 +7225,48 @@
       <c r="D66" s="2" t="n">
         <v>614.25</v>
       </c>
-      <c r="E66" s="3" t="n"/>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="n">
         <v>1383.2</v>
       </c>
-      <c r="G66" s="3" t="n"/>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="I66" s="3" t="n"/>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="n">
         <v>1137.5</v>
       </c>
-      <c r="K66" s="3" t="n"/>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M66" s="3" t="n"/>
+      <c r="M66" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5997,31 +7289,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E67" s="3" t="n"/>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G67" s="3" t="n"/>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I67" s="3" t="n"/>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K67" s="3" t="n"/>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M67" s="3" t="n"/>
+      <c r="M67" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6042,23 +7359,48 @@
       <c r="D68" s="2" t="n">
         <v>250.25</v>
       </c>
-      <c r="E68" s="3" t="n"/>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="G68" s="3" t="n"/>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="n">
         <v>500.5</v>
       </c>
-      <c r="I68" s="3" t="n"/>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="K68" s="3" t="n"/>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="n">
         <v>471.107</v>
       </c>
-      <c r="M68" s="3" t="n"/>
+      <c r="M68" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6079,23 +7421,48 @@
       <c r="D69" s="2" t="n">
         <v>7.007</v>
       </c>
-      <c r="E69" s="3" t="n"/>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="n">
         <v>14.651</v>
       </c>
-      <c r="G69" s="3" t="n"/>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="n">
         <v>11.466</v>
       </c>
-      <c r="I69" s="3" t="n"/>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="K69" s="3" t="n"/>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L69" s="2" t="n">
         <v>11.557</v>
       </c>
-      <c r="M69" s="3" t="n"/>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -6116,23 +7483,48 @@
       <c r="D70" s="2" t="n">
         <v>546</v>
       </c>
-      <c r="E70" s="3" t="n"/>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="n">
         <v>1001</v>
       </c>
-      <c r="G70" s="3" t="n"/>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="I70" s="3" t="n"/>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="n">
         <v>486.122</v>
       </c>
-      <c r="K70" s="3" t="n"/>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L70" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M70" s="3" t="n"/>
+      <c r="M70" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6155,29 +7547,54 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E71" s="3" t="n"/>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="G71" s="3" t="n"/>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I71" s="3" t="n"/>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K71" s="3" t="n"/>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M71" s="3" t="n"/>
+      <c r="M71" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -6198,23 +7615,48 @@
       <c r="D72" s="2" t="n">
         <v>295.75</v>
       </c>
-      <c r="E72" s="3" t="n"/>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="n">
         <v>750.75</v>
       </c>
-      <c r="G72" s="3" t="n"/>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="n">
         <v>579.67</v>
       </c>
-      <c r="I72" s="3" t="n"/>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="K72" s="3" t="n"/>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="M72" s="3" t="n"/>
+      <c r="M72" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -6237,29 +7679,54 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E73" s="3" t="n"/>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="n">
         <v>1592.5</v>
       </c>
-      <c r="G73" s="3" t="n"/>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I73" s="3" t="n"/>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K73" s="3" t="n"/>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M73" s="3" t="n"/>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -6280,23 +7747,48 @@
       <c r="D74" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E74" s="3" t="n"/>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="n">
         <v>1319.5</v>
       </c>
-      <c r="G74" s="3" t="n"/>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="n">
         <v>690.6900000000001</v>
       </c>
-      <c r="I74" s="3" t="n"/>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="K74" s="3" t="n"/>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M74" s="3" t="n"/>
+      <c r="M74" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -6317,23 +7809,48 @@
       <c r="D75" s="2" t="n">
         <v>250.25</v>
       </c>
-      <c r="E75" s="3" t="n"/>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="n">
         <v>482.3</v>
       </c>
-      <c r="G75" s="3" t="n"/>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="n">
         <v>359.45</v>
       </c>
-      <c r="I75" s="3" t="n"/>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="n">
         <v>663.936</v>
       </c>
-      <c r="K75" s="3" t="n"/>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L75" s="2" t="n">
         <v>249.34</v>
       </c>
-      <c r="M75" s="3" t="n"/>
+      <c r="M75" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -6356,31 +7873,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E76" s="3" t="n"/>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G76" s="3" t="n"/>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I76" s="3" t="n"/>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K76" s="3" t="n"/>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M76" s="3" t="n"/>
+      <c r="M76" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -6401,23 +7943,48 @@
       <c r="D77" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E77" s="3" t="n"/>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F77" s="2" t="n">
         <v>1501.5</v>
       </c>
-      <c r="G77" s="3" t="n"/>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="n">
         <v>705.25</v>
       </c>
-      <c r="I77" s="3" t="n"/>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="n">
         <v>546</v>
       </c>
-      <c r="K77" s="3" t="n"/>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L77" s="2" t="n">
         <v>318.5</v>
       </c>
-      <c r="M77" s="3" t="n"/>
+      <c r="M77" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -6438,23 +8005,48 @@
       <c r="D78" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E78" s="3" t="n"/>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="n">
         <v>955.5</v>
       </c>
-      <c r="G78" s="3" t="n"/>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I78" s="3" t="n"/>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="K78" s="3" t="n"/>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L78" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M78" s="3" t="n"/>
+      <c r="M78" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6475,23 +8067,48 @@
       <c r="D79" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="E79" s="3" t="n"/>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="n">
         <v>2457</v>
       </c>
-      <c r="G79" s="3" t="n"/>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="I79" s="3" t="n"/>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="K79" s="3" t="n"/>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L79" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="M79" s="3" t="n"/>
+      <c r="M79" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6531,6 +8148,11 @@
         <v>24.752</v>
       </c>
       <c r="M80" s="3" t="n"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -6570,6 +8192,11 @@
         <v>24.115</v>
       </c>
       <c r="M81" s="3" t="n"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6615,6 +8242,11 @@
         </is>
       </c>
       <c r="M82" s="3" t="n"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6658,6 +8290,11 @@
         <v>1.774</v>
       </c>
       <c r="M83" s="3" t="n"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6697,6 +8334,11 @@
         <v>0.637</v>
       </c>
       <c r="M84" s="3" t="n"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6734,6 +8376,11 @@
         <v>409.5</v>
       </c>
       <c r="M85" s="3" t="n"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6781,6 +8428,11 @@
         </is>
       </c>
       <c r="M86" s="3" t="n"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6820,6 +8472,11 @@
         <v>1456</v>
       </c>
       <c r="M87" s="3" t="n"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6859,6 +8516,11 @@
         </is>
       </c>
       <c r="M88" s="3" t="n"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6906,6 +8568,11 @@
         </is>
       </c>
       <c r="M89" s="3" t="n"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6953,6 +8620,11 @@
         </is>
       </c>
       <c r="M90" s="3" t="n"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6992,6 +8664,11 @@
         <v>2.73</v>
       </c>
       <c r="M91" s="3" t="n"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -7031,6 +8708,11 @@
         <v>2.73</v>
       </c>
       <c r="M92" s="3" t="n"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -7070,6 +8752,11 @@
         <v>4.55</v>
       </c>
       <c r="M93" s="3" t="n"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -7109,6 +8796,11 @@
         <v>0.91</v>
       </c>
       <c r="M94" s="3" t="n"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7154,6 +8846,11 @@
         </is>
       </c>
       <c r="M95" s="3" t="n"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -7201,6 +8898,11 @@
         </is>
       </c>
       <c r="M96" s="3" t="n"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -7240,6 +8942,11 @@
         <v>22.477</v>
       </c>
       <c r="M97" s="3" t="n"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7287,6 +8994,11 @@
         </is>
       </c>
       <c r="M98" s="3" t="n"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7326,6 +9038,11 @@
         <v>18.564</v>
       </c>
       <c r="M99" s="3" t="n"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7365,6 +9082,11 @@
         <v>24.752</v>
       </c>
       <c r="M100" s="3" t="n"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7404,6 +9126,11 @@
         <v>0.91</v>
       </c>
       <c r="M101" s="3" t="n"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7451,6 +9178,11 @@
         </is>
       </c>
       <c r="M102" s="3" t="n"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -7490,6 +9222,11 @@
         <v>9.1</v>
       </c>
       <c r="M103" s="3" t="n"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -7529,6 +9266,11 @@
         <v>23.205</v>
       </c>
       <c r="M104" s="3" t="n"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7572,6 +9314,11 @@
         </is>
       </c>
       <c r="M105" s="3" t="n"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7611,6 +9358,11 @@
         <v>4.368</v>
       </c>
       <c r="M106" s="3" t="n"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -7650,6 +9402,11 @@
         <v>15.47</v>
       </c>
       <c r="M107" s="3" t="n"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Sawhney Foodstuff TR. CO. LLC SP</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7687,6 +9444,11 @@
         <v>7.28</v>
       </c>
       <c r="M108" s="3" t="n"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7724,6 +9486,11 @@
         <v>6.37</v>
       </c>
       <c r="M109" s="3" t="n"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7761,6 +9528,11 @@
         <v>291.2</v>
       </c>
       <c r="M110" s="3" t="n"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7802,6 +9574,11 @@
         </is>
       </c>
       <c r="M111" s="3" t="n"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7839,6 +9616,11 @@
         <v>16.38</v>
       </c>
       <c r="M112" s="3" t="n"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7876,6 +9658,11 @@
         <v>3.64</v>
       </c>
       <c r="M113" s="3" t="n"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7913,6 +9700,11 @@
         <v>7.508</v>
       </c>
       <c r="M114" s="3" t="n"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7960,6 +9752,11 @@
         </is>
       </c>
       <c r="M115" s="3" t="n"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7997,6 +9794,11 @@
         <v>0.673</v>
       </c>
       <c r="M116" s="3" t="n"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -8034,6 +9836,11 @@
         <v>1.17</v>
       </c>
       <c r="M117" s="3" t="n"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -8071,6 +9878,11 @@
         <v>1.17</v>
       </c>
       <c r="M118" s="3" t="n"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8118,6 +9930,11 @@
         </is>
       </c>
       <c r="M119" s="3" t="n"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8155,6 +9972,11 @@
         <v>0.965</v>
       </c>
       <c r="M120" s="3" t="n"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8192,6 +10014,11 @@
         <v>1.17</v>
       </c>
       <c r="M121" s="3" t="n"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -8229,6 +10056,11 @@
         <v>0.234</v>
       </c>
       <c r="M122" s="3" t="n"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8266,6 +10098,11 @@
         <v>0.117</v>
       </c>
       <c r="M123" s="3" t="n"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -8303,6 +10140,11 @@
         <v>17.55</v>
       </c>
       <c r="M124" s="3" t="n"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -8340,6 +10182,11 @@
         <v>0.309</v>
       </c>
       <c r="M125" s="3" t="n"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -8377,6 +10224,11 @@
         <v>43.225</v>
       </c>
       <c r="M126" s="3" t="n"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8422,6 +10274,11 @@
         </is>
       </c>
       <c r="M127" s="3" t="n"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8459,6 +10316,11 @@
         <v>91</v>
       </c>
       <c r="M128" s="3" t="n"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8496,6 +10358,11 @@
         <v>0.673</v>
       </c>
       <c r="M129" s="3" t="n"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8533,6 +10400,11 @@
         <v>1.529</v>
       </c>
       <c r="M130" s="3" t="n"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8570,6 +10442,11 @@
         <v>3.367</v>
       </c>
       <c r="M131" s="3" t="n"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8607,6 +10484,11 @@
         <v>0.346</v>
       </c>
       <c r="M132" s="3" t="n"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8644,6 +10526,11 @@
         <v>0.91</v>
       </c>
       <c r="M133" s="3" t="n"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8681,6 +10568,11 @@
         <v>0.662</v>
       </c>
       <c r="M134" s="3" t="n"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8718,6 +10610,11 @@
         <v>91</v>
       </c>
       <c r="M135" s="3" t="n"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8765,6 +10662,11 @@
         </is>
       </c>
       <c r="M136" s="3" t="n"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8802,6 +10704,11 @@
         <v>245.7</v>
       </c>
       <c r="M137" s="3" t="n"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8847,6 +10754,11 @@
         <v>0.234</v>
       </c>
       <c r="M138" s="3" t="n"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8884,6 +10796,11 @@
         <v>0.346</v>
       </c>
       <c r="M139" s="3" t="n"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8931,6 +10848,11 @@
         </is>
       </c>
       <c r="M140" s="3" t="n"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8968,6 +10890,11 @@
         <v>1.365</v>
       </c>
       <c r="M141" s="3" t="n"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9005,6 +10932,11 @@
         <v>0.819</v>
       </c>
       <c r="M142" s="3" t="n"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Sunberry</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -9027,31 +10959,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E143" s="3" t="n"/>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G143" s="3" t="n"/>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I143" s="3" t="n"/>
+      <c r="I143" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K143" s="3" t="n"/>
+      <c r="K143" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M143" s="3" t="n"/>
+      <c r="M143" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -9072,23 +11029,48 @@
       <c r="D144" s="2" t="n">
         <v>227.5</v>
       </c>
-      <c r="E144" s="3" t="n"/>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F144" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="G144" s="3" t="n"/>
+      <c r="G144" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="n">
         <v>240.968</v>
       </c>
-      <c r="I144" s="3" t="n"/>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J144" s="2" t="n">
         <v>457.73</v>
       </c>
-      <c r="K144" s="3" t="n"/>
+      <c r="K144" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L144" s="2" t="n">
         <v>391.3</v>
       </c>
-      <c r="M144" s="3" t="n"/>
+      <c r="M144" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9109,23 +11091,48 @@
       <c r="D145" s="2" t="n">
         <v>250.25</v>
       </c>
-      <c r="E145" s="3" t="n"/>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F145" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="G145" s="3" t="n"/>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="n">
         <v>273</v>
       </c>
-      <c r="I145" s="3" t="n"/>
+      <c r="I145" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J145" s="2" t="n">
         <v>436.345</v>
       </c>
-      <c r="K145" s="3" t="n"/>
+      <c r="K145" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L145" s="2" t="n">
         <v>507.78</v>
       </c>
-      <c r="M145" s="3" t="n"/>
+      <c r="M145" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9146,23 +11153,48 @@
       <c r="D146" s="2" t="n">
         <v>591.5</v>
       </c>
-      <c r="E146" s="3" t="n"/>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F146" s="2" t="n">
         <v>518.7</v>
       </c>
-      <c r="G146" s="3" t="n"/>
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I146" s="3" t="n"/>
+      <c r="I146" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J146" s="2" t="n">
         <v>480.48</v>
       </c>
-      <c r="K146" s="3" t="n"/>
+      <c r="K146" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L146" s="2" t="n">
         <v>456.82</v>
       </c>
-      <c r="M146" s="3" t="n"/>
+      <c r="M146" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9185,31 +11217,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E147" s="3" t="n"/>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G147" s="3" t="n"/>
+      <c r="G147" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I147" s="3" t="n"/>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K147" s="3" t="n"/>
+      <c r="K147" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M147" s="3" t="n"/>
+      <c r="M147" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9230,23 +11287,48 @@
       <c r="D148" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="E148" s="3" t="n"/>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F148" s="2" t="n">
         <v>966.966</v>
       </c>
-      <c r="G148" s="3" t="n"/>
+      <c r="G148" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="n">
         <v>618.8</v>
       </c>
-      <c r="I148" s="3" t="n"/>
+      <c r="I148" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J148" s="2" t="n">
         <v>818.09</v>
       </c>
-      <c r="K148" s="3" t="n"/>
+      <c r="K148" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L148" s="2" t="n">
         <v>690.6900000000001</v>
       </c>
-      <c r="M148" s="3" t="n"/>
+      <c r="M148" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9269,31 +11351,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E149" s="3" t="n"/>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G149" s="3" t="n"/>
+      <c r="G149" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I149" s="3" t="n"/>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K149" s="3" t="n"/>
+      <c r="K149" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M149" s="3" t="n"/>
+      <c r="M149" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9314,23 +11421,48 @@
       <c r="D150" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="E150" s="3" t="n"/>
+      <c r="E150" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F150" s="2" t="n">
         <v>955.5</v>
       </c>
-      <c r="G150" s="3" t="n"/>
+      <c r="G150" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="I150" s="3" t="n"/>
+      <c r="I150" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J150" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="K150" s="3" t="n"/>
+      <c r="K150" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L150" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="M150" s="3" t="n"/>
+      <c r="M150" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9353,27 +11485,52 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E151" s="3" t="n"/>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F151" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="G151" s="3" t="n"/>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I151" s="3" t="n"/>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K151" s="3" t="n"/>
+      <c r="K151" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M151" s="3" t="n"/>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9394,23 +11551,48 @@
       <c r="D152" s="2" t="n">
         <v>568.75</v>
       </c>
-      <c r="E152" s="3" t="n"/>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F152" s="2" t="n">
         <v>418.6</v>
       </c>
-      <c r="G152" s="3" t="n"/>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="n">
         <v>227.5</v>
       </c>
-      <c r="I152" s="3" t="n"/>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J152" s="2" t="n">
         <v>227.5</v>
       </c>
-      <c r="K152" s="3" t="n"/>
+      <c r="K152" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L152" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M152" s="3" t="n"/>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9431,23 +11613,48 @@
       <c r="D153" s="2" t="n">
         <v>227.5</v>
       </c>
-      <c r="E153" s="3" t="n"/>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F153" s="2" t="n">
         <v>509.6</v>
       </c>
-      <c r="G153" s="3" t="n"/>
+      <c r="G153" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I153" s="3" t="n"/>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J153" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="K153" s="3" t="n"/>
+      <c r="K153" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L153" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M153" s="3" t="n"/>
+      <c r="M153" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -9468,23 +11675,48 @@
       <c r="D154" s="2" t="n">
         <v>250.25</v>
       </c>
-      <c r="E154" s="3" t="n"/>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F154" s="2" t="n">
         <v>1173.9</v>
       </c>
-      <c r="G154" s="3" t="n"/>
+      <c r="G154" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I154" s="3" t="n"/>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J154" s="2" t="n">
         <v>467.649</v>
       </c>
-      <c r="K154" s="3" t="n"/>
+      <c r="K154" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L154" s="2" t="n">
         <v>500.5</v>
       </c>
-      <c r="M154" s="3" t="n"/>
+      <c r="M154" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -9505,23 +11737,48 @@
       <c r="D155" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E155" s="3" t="n"/>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F155" s="2" t="n">
         <v>691.6</v>
       </c>
-      <c r="G155" s="3" t="n"/>
+      <c r="G155" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="I155" s="3" t="n"/>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J155" s="2" t="n">
         <v>728</v>
       </c>
-      <c r="K155" s="3" t="n"/>
+      <c r="K155" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L155" s="2" t="n">
         <v>869.05</v>
       </c>
-      <c r="M155" s="3" t="n"/>
+      <c r="M155" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9542,23 +11799,48 @@
       <c r="D156" s="2" t="n">
         <v>273</v>
       </c>
-      <c r="E156" s="3" t="n"/>
+      <c r="E156" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F156" s="2" t="n">
         <v>728</v>
       </c>
-      <c r="G156" s="3" t="n"/>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I156" s="3" t="n"/>
+      <c r="I156" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J156" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="K156" s="3" t="n"/>
+      <c r="K156" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L156" s="2" t="n">
         <v>532.35</v>
       </c>
-      <c r="M156" s="3" t="n"/>
+      <c r="M156" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -9579,23 +11861,48 @@
       <c r="D157" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="E157" s="3" t="n"/>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F157" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="G157" s="3" t="n"/>
+      <c r="G157" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I157" s="3" t="n"/>
+      <c r="I157" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J157" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="K157" s="3" t="n"/>
+      <c r="K157" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L157" s="2" t="n">
         <v>955.5</v>
       </c>
-      <c r="M157" s="3" t="n"/>
+      <c r="M157" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -9616,23 +11923,48 @@
       <c r="D158" s="2" t="n">
         <v>345.8</v>
       </c>
-      <c r="E158" s="3" t="n"/>
+      <c r="E158" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F158" s="2" t="n">
         <v>664.3</v>
       </c>
-      <c r="G158" s="3" t="n"/>
+      <c r="G158" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="n">
         <v>463.19</v>
       </c>
-      <c r="I158" s="3" t="n"/>
+      <c r="I158" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J158" s="2" t="n">
         <v>662.025</v>
       </c>
-      <c r="K158" s="3" t="n"/>
+      <c r="K158" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L158" s="2" t="n">
         <v>485.03</v>
       </c>
-      <c r="M158" s="3" t="n"/>
+      <c r="M158" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -9653,23 +11985,48 @@
       <c r="D159" s="2" t="n">
         <v>2047.5</v>
       </c>
-      <c r="E159" s="3" t="n"/>
+      <c r="E159" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F159" s="2" t="n">
         <v>2566.2</v>
       </c>
-      <c r="G159" s="3" t="n"/>
+      <c r="G159" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="n">
         <v>1774.5</v>
       </c>
-      <c r="I159" s="3" t="n"/>
+      <c r="I159" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J159" s="2" t="n">
         <v>1774.5</v>
       </c>
-      <c r="K159" s="3" t="n"/>
+      <c r="K159" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L159" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="M159" s="3" t="n"/>
+      <c r="M159" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9690,23 +12047,48 @@
       <c r="D160" s="2" t="n">
         <v>432.25</v>
       </c>
-      <c r="E160" s="3" t="n"/>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F160" s="2" t="n">
         <v>1001</v>
       </c>
-      <c r="G160" s="3" t="n"/>
+      <c r="G160" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I160" s="3" t="n"/>
+      <c r="I160" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J160" s="2" t="n">
         <v>651.5599999999999</v>
       </c>
-      <c r="K160" s="3" t="n"/>
+      <c r="K160" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L160" s="2" t="n">
         <v>739.83</v>
       </c>
-      <c r="M160" s="3" t="n"/>
+      <c r="M160" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9729,31 +12111,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E161" s="3" t="n"/>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G161" s="3" t="n"/>
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I161" s="3" t="n"/>
+      <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K161" s="3" t="n"/>
+      <c r="K161" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L161" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M161" s="3" t="n"/>
+      <c r="M161" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9774,23 +12181,48 @@
       <c r="D162" s="2" t="n">
         <v>382.2</v>
       </c>
-      <c r="E162" s="3" t="n"/>
+      <c r="E162" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F162" s="2" t="n">
         <v>500.5</v>
       </c>
-      <c r="G162" s="3" t="n"/>
+      <c r="G162" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="n">
         <v>227.5</v>
       </c>
-      <c r="I162" s="3" t="n"/>
+      <c r="I162" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J162" s="2" t="n">
         <v>497.952</v>
       </c>
-      <c r="K162" s="3" t="n"/>
+      <c r="K162" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L162" s="2" t="n">
         <v>263.9</v>
       </c>
-      <c r="M162" s="3" t="n"/>
+      <c r="M162" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9811,23 +12243,48 @@
       <c r="D163" s="2" t="n">
         <v>728</v>
       </c>
-      <c r="E163" s="3" t="n"/>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F163" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="G163" s="3" t="n"/>
+      <c r="G163" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H163" s="2" t="n">
         <v>273</v>
       </c>
-      <c r="I163" s="3" t="n"/>
+      <c r="I163" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J163" s="2" t="n">
         <v>172.445</v>
       </c>
-      <c r="K163" s="3" t="n"/>
+      <c r="K163" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L163" s="2" t="n">
         <v>200.2</v>
       </c>
-      <c r="M163" s="3" t="n"/>
+      <c r="M163" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9848,23 +12305,48 @@
       <c r="D164" s="2" t="n">
         <v>5460</v>
       </c>
-      <c r="E164" s="3" t="n"/>
+      <c r="E164" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F164" s="2" t="n">
         <v>18.655</v>
       </c>
-      <c r="G164" s="3" t="n"/>
+      <c r="G164" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H164" s="2" t="n">
         <v>8192.548000000001</v>
       </c>
-      <c r="I164" s="3" t="n"/>
+      <c r="I164" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J164" s="2" t="n">
         <v>17.836</v>
       </c>
-      <c r="K164" s="3" t="n"/>
+      <c r="K164" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L164" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="M164" s="3" t="n"/>
+      <c r="M164" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9885,23 +12367,48 @@
       <c r="D165" s="2" t="n">
         <v>568.75</v>
       </c>
-      <c r="E165" s="3" t="n"/>
+      <c r="E165" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F165" s="2" t="n">
         <v>955.5</v>
       </c>
-      <c r="G165" s="3" t="n"/>
+      <c r="G165" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H165" s="2" t="n">
         <v>677.95</v>
       </c>
-      <c r="I165" s="3" t="n"/>
+      <c r="I165" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J165" s="2" t="n">
         <v>700.8819999999999</v>
       </c>
-      <c r="K165" s="3" t="n"/>
+      <c r="K165" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L165" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="M165" s="3" t="n"/>
+      <c r="M165" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9922,23 +12429,48 @@
       <c r="D166" s="2" t="n">
         <v>2275</v>
       </c>
-      <c r="E166" s="3" t="n"/>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F166" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="G166" s="3" t="n"/>
+      <c r="G166" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="I166" s="3" t="n"/>
+      <c r="I166" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J166" s="2" t="n">
         <v>1365</v>
       </c>
-      <c r="K166" s="3" t="n"/>
+      <c r="K166" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L166" s="2" t="n">
         <v>1820</v>
       </c>
-      <c r="M166" s="3" t="n"/>
+      <c r="M166" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -9961,27 +12493,52 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E167" s="3" t="n"/>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F167" s="2" t="n">
         <v>229.775</v>
       </c>
-      <c r="G167" s="3" t="n"/>
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H167" s="2" t="n">
         <v>1032.85</v>
       </c>
-      <c r="I167" s="3" t="n"/>
+      <c r="I167" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K167" s="3" t="n"/>
+      <c r="K167" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M167" s="3" t="n"/>
+      <c r="M167" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -10002,23 +12559,48 @@
       <c r="D168" s="2" t="n">
         <v>568.75</v>
       </c>
-      <c r="E168" s="3" t="n"/>
+      <c r="E168" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F168" s="2" t="n">
         <v>1092</v>
       </c>
-      <c r="G168" s="3" t="n"/>
+      <c r="G168" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H168" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="I168" s="3" t="n"/>
+      <c r="I168" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J168" s="2" t="n">
         <v>891.8</v>
       </c>
-      <c r="K168" s="3" t="n"/>
+      <c r="K168" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L168" s="2" t="n">
         <v>1428.7</v>
       </c>
-      <c r="M168" s="3" t="n"/>
+      <c r="M168" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10041,31 +12623,56 @@
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="E169" s="3" t="n"/>
+      <c r="E169" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="G169" s="3" t="n"/>
+      <c r="G169" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="I169" s="3" t="n"/>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="K169" s="3" t="n"/>
+      <c r="K169" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
           <t>← 未設定</t>
         </is>
       </c>
-      <c r="M169" s="3" t="n"/>
+      <c r="M169" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -10086,23 +12693,48 @@
       <c r="D170" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="E170" s="3" t="n"/>
+      <c r="E170" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F170" s="2" t="n">
         <v>837.2</v>
       </c>
-      <c r="G170" s="3" t="n"/>
+      <c r="G170" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H170" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="I170" s="3" t="n"/>
+      <c r="I170" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J170" s="2" t="n">
         <v>682.5</v>
       </c>
-      <c r="K170" s="3" t="n"/>
+      <c r="K170" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L170" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="M170" s="3" t="n"/>
+      <c r="M170" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -10123,23 +12755,48 @@
       <c r="D171" s="2" t="n">
         <v>145.6</v>
       </c>
-      <c r="E171" s="3" t="n"/>
+      <c r="E171" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="F171" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="G171" s="3" t="n"/>
+      <c r="G171" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="H171" s="2" t="n">
         <v>45.5</v>
       </c>
-      <c r="I171" s="3" t="n"/>
+      <c r="I171" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="J171" s="2" t="n">
         <v>495.04</v>
       </c>
-      <c r="K171" s="3" t="n"/>
+      <c r="K171" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="L171" s="2" t="n">
         <v>329.42</v>
       </c>
-      <c r="M171" s="3" t="n"/>
+      <c r="M171" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Central Kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -10177,6 +12834,11 @@
         <v>111.02</v>
       </c>
       <c r="M172" s="3" t="n"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Taste Masters</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10224,6 +12886,11 @@
         </is>
       </c>
       <c r="M173" s="3" t="n"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10261,6 +12928,11 @@
         <v>3823.911</v>
       </c>
       <c r="M174" s="3" t="n"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -10298,6 +12970,11 @@
         <v>36.4</v>
       </c>
       <c r="M175" s="3" t="n"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10345,6 +13022,11 @@
         </is>
       </c>
       <c r="M176" s="3" t="n"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -10392,6 +13074,11 @@
         </is>
       </c>
       <c r="M177" s="3" t="n"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10439,6 +13126,11 @@
         </is>
       </c>
       <c r="M178" s="3" t="n"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -10486,6 +13178,11 @@
         </is>
       </c>
       <c r="M179" s="3" t="n"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -10533,6 +13230,11 @@
         </is>
       </c>
       <c r="M180" s="3" t="n"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -10570,6 +13272,11 @@
         <v>2.457</v>
       </c>
       <c r="M181" s="3" t="n"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10607,6 +13314,11 @@
         <v>18.2</v>
       </c>
       <c r="M182" s="3" t="n"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Taste Masters</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -10644,6 +13356,11 @@
         <v>591.5</v>
       </c>
       <c r="M183" s="3" t="n"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Taste Masters</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10681,6 +13398,11 @@
         <v>36.4</v>
       </c>
       <c r="M184" s="3" t="n"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Taste Masters</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -10718,6 +13440,11 @@
         <v>728</v>
       </c>
       <c r="M185" s="3" t="n"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Taste Masters</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10765,6 +13492,11 @@
         </is>
       </c>
       <c r="M186" s="3" t="n"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -10802,6 +13534,11 @@
         <v>5.46</v>
       </c>
       <c r="M187" s="3" t="n"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Taste Masters</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -10849,6 +13586,11 @@
         </is>
       </c>
       <c r="M188" s="3" t="n"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Taste Masters LLC</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -10886,6 +13628,11 @@
         <v>1456.364</v>
       </c>
       <c r="M189" s="3" t="n"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Taste Masters</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -10923,6 +13670,11 @@
         <v>1237.6</v>
       </c>
       <c r="M190" s="3" t="n"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10960,6 +13712,11 @@
         <v>910</v>
       </c>
       <c r="M191" s="3" t="n"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -10997,6 +13754,11 @@
         <v>81.90000000000001</v>
       </c>
       <c r="M192" s="3" t="n"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -11034,6 +13796,11 @@
         <v>338.52</v>
       </c>
       <c r="M193" s="3" t="n"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -11071,6 +13838,11 @@
         <v>141.96</v>
       </c>
       <c r="M194" s="3" t="n"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -11118,6 +13890,11 @@
         </is>
       </c>
       <c r="M195" s="3" t="n"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -11155,6 +13932,11 @@
         <v>2.457</v>
       </c>
       <c r="M196" s="3" t="n"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -11192,6 +13974,11 @@
         <v>1.82</v>
       </c>
       <c r="M197" s="3" t="n"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -11229,6 +14016,11 @@
         <v>2.73</v>
       </c>
       <c r="M198" s="3" t="n"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -11276,6 +14068,11 @@
         </is>
       </c>
       <c r="M199" s="3" t="n"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -11323,6 +14120,11 @@
         </is>
       </c>
       <c r="M200" s="3" t="n"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>J Deli</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -11360,6 +14162,11 @@
         <v>70.52500000000001</v>
       </c>
       <c r="M201" s="3" t="n"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -11397,6 +14204,11 @@
         <v>5.369</v>
       </c>
       <c r="M202" s="3" t="n"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -11434,6 +14246,11 @@
         <v>5.551</v>
       </c>
       <c r="M203" s="3" t="n"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -11473,6 +14290,11 @@
         <v>2.73</v>
       </c>
       <c r="M204" s="3" t="n"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -11510,6 +14332,11 @@
         <v>3.64</v>
       </c>
       <c r="M205" s="3" t="n"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -11547,6 +14374,11 @@
         <v>637</v>
       </c>
       <c r="M206" s="3" t="n"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -11588,6 +14420,11 @@
         <v>0.91</v>
       </c>
       <c r="M207" s="3" t="n"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -11625,6 +14462,11 @@
         <v>2.093</v>
       </c>
       <c r="M208" s="3" t="n"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -11662,6 +14504,11 @@
         <v>1.82</v>
       </c>
       <c r="M209" s="3" t="n"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -11699,6 +14546,11 @@
         <v>2.73</v>
       </c>
       <c r="M210" s="3" t="n"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -11736,6 +14588,11 @@
         <v>2.184</v>
       </c>
       <c r="M211" s="3" t="n"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -11773,6 +14630,11 @@
         <v>22.75</v>
       </c>
       <c r="M212" s="3" t="n"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -11814,6 +14676,11 @@
         </is>
       </c>
       <c r="M213" s="3" t="n"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -11851,6 +14718,11 @@
         <v>718.9</v>
       </c>
       <c r="M214" s="3" t="n"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -11888,6 +14760,11 @@
         <v>6.37</v>
       </c>
       <c r="M215" s="3" t="n"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -11925,6 +14802,11 @@
         <v>2.73</v>
       </c>
       <c r="M216" s="3" t="n"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -11962,6 +14844,11 @@
         <v>45.5</v>
       </c>
       <c r="M217" s="3" t="n"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -11999,6 +14886,11 @@
         <v>50.05</v>
       </c>
       <c r="M218" s="3" t="n"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -12042,6 +14934,11 @@
         </is>
       </c>
       <c r="M219" s="3" t="n"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -12079,6 +14976,11 @@
         <v>3.64</v>
       </c>
       <c r="M220" s="3" t="n"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -12126,6 +15028,11 @@
         </is>
       </c>
       <c r="M221" s="3" t="n"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -12173,6 +15080,11 @@
         </is>
       </c>
       <c r="M222" s="3" t="n"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -12210,6 +15122,11 @@
         <v>136.5</v>
       </c>
       <c r="M223" s="3" t="n"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -12247,6 +15164,11 @@
         <v>136.5</v>
       </c>
       <c r="M224" s="3" t="n"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -12284,6 +15206,11 @@
         <v>136.5</v>
       </c>
       <c r="M225" s="3" t="n"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -12321,6 +15248,11 @@
         <v>225.134</v>
       </c>
       <c r="M226" s="3" t="n"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -12358,6 +15290,11 @@
         <v>224.861</v>
       </c>
       <c r="M227" s="3" t="n"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -12395,6 +15332,11 @@
         <v>223.86</v>
       </c>
       <c r="M228" s="3" t="n"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -12432,6 +15374,11 @@
         <v>223.769</v>
       </c>
       <c r="M229" s="3" t="n"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -12479,6 +15426,11 @@
         </is>
       </c>
       <c r="M230" s="3" t="n"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -12516,6 +15468,11 @@
         <v>200.2</v>
       </c>
       <c r="M231" s="3" t="n"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -12553,6 +15510,11 @@
         <v>245.7</v>
       </c>
       <c r="M232" s="3" t="n"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -12590,6 +15552,11 @@
         <v>209.3</v>
       </c>
       <c r="M233" s="3" t="n"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -12627,6 +15594,11 @@
         <v>57.785</v>
       </c>
       <c r="M234" s="3" t="n"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -12664,6 +15636,11 @@
         <v>4.55</v>
       </c>
       <c r="M235" s="3" t="n"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -12711,6 +15688,11 @@
         </is>
       </c>
       <c r="M236" s="3" t="n"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -12758,6 +15740,11 @@
         </is>
       </c>
       <c r="M237" s="3" t="n"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -12805,6 +15792,11 @@
         </is>
       </c>
       <c r="M238" s="3" t="n"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -12852,6 +15844,11 @@
         </is>
       </c>
       <c r="M239" s="3" t="n"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -12899,6 +15896,11 @@
         </is>
       </c>
       <c r="M240" s="3" t="n"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -12936,6 +15938,11 @@
         <v>177.45</v>
       </c>
       <c r="M241" s="3" t="n"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -12981,6 +15988,11 @@
         </is>
       </c>
       <c r="M242" s="3" t="n"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -13018,6 +16030,11 @@
         <v>95.55</v>
       </c>
       <c r="M243" s="3" t="n"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -13055,6 +16072,11 @@
         <v>72.8</v>
       </c>
       <c r="M244" s="3" t="n"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -13102,6 +16124,11 @@
         </is>
       </c>
       <c r="M245" s="3" t="n"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -13149,6 +16176,11 @@
         </is>
       </c>
       <c r="M246" s="3" t="n"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -13196,6 +16228,11 @@
         </is>
       </c>
       <c r="M247" s="3" t="n"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -13243,6 +16280,11 @@
         </is>
       </c>
       <c r="M248" s="3" t="n"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -13290,6 +16332,11 @@
         </is>
       </c>
       <c r="M249" s="3" t="n"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -13337,6 +16384,11 @@
         </is>
       </c>
       <c r="M250" s="3" t="n"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -13384,6 +16436,11 @@
         </is>
       </c>
       <c r="M251" s="3" t="n"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -13431,6 +16488,11 @@
         </is>
       </c>
       <c r="M252" s="3" t="n"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -13474,6 +16536,11 @@
         <v>455</v>
       </c>
       <c r="M253" s="3" t="n"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -13511,6 +16578,11 @@
         <v>809.9</v>
       </c>
       <c r="M254" s="3" t="n"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -13558,6 +16630,11 @@
         </is>
       </c>
       <c r="M255" s="3" t="n"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -13595,6 +16672,11 @@
         <v>546</v>
       </c>
       <c r="M256" s="3" t="n"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -13634,6 +16716,11 @@
         </is>
       </c>
       <c r="M257" s="3" t="n"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -13671,6 +16758,11 @@
         <v>138.32</v>
       </c>
       <c r="M258" s="3" t="n"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -13718,6 +16810,11 @@
         </is>
       </c>
       <c r="M259" s="3" t="n"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -13755,6 +16852,11 @@
         <v>45.5</v>
       </c>
       <c r="M260" s="3" t="n"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -13792,6 +16894,11 @@
         <v>263.9</v>
       </c>
       <c r="M261" s="3" t="n"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -13839,6 +16946,11 @@
         </is>
       </c>
       <c r="M262" s="3" t="n"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -13886,6 +16998,11 @@
         </is>
       </c>
       <c r="M263" s="3" t="n"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -13933,6 +17050,11 @@
         </is>
       </c>
       <c r="M264" s="3" t="n"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -13974,6 +17096,11 @@
         <v>45.5</v>
       </c>
       <c r="M265" s="3" t="n"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -14011,6 +17138,11 @@
         <v>86.45</v>
       </c>
       <c r="M266" s="3" t="n"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -14048,6 +17180,11 @@
         <v>273</v>
       </c>
       <c r="M267" s="3" t="n"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -14085,6 +17222,11 @@
         <v>3.64</v>
       </c>
       <c r="M268" s="3" t="n"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -14122,6 +17264,11 @@
         <v>18.2</v>
       </c>
       <c r="M269" s="3" t="n"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -14169,6 +17316,11 @@
         </is>
       </c>
       <c r="M270" s="3" t="n"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -14212,6 +17364,11 @@
         </is>
       </c>
       <c r="M271" s="3" t="n"/>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -14255,6 +17412,11 @@
         </is>
       </c>
       <c r="M272" s="3" t="n"/>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -14292,6 +17454,11 @@
         <v>95.55</v>
       </c>
       <c r="M273" s="3" t="n"/>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -14329,6 +17496,11 @@
         <v>131.95</v>
       </c>
       <c r="M274" s="3" t="n"/>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -14366,6 +17538,11 @@
         <v>9.009</v>
       </c>
       <c r="M275" s="3" t="n"/>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -14403,6 +17580,11 @@
         <v>10.374</v>
       </c>
       <c r="M276" s="3" t="n"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -14442,6 +17624,11 @@
         <v>27.664</v>
       </c>
       <c r="M277" s="3" t="n"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Sushi ZEN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
